--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,11 +542,11 @@
         <v>240000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-20 22:41:20</t>
+          <t>2026-10-20 23:33:51</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1980,6 +1980,98 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:33:51</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:33:51</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>240000</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -542,11 +542,11 @@
         <v>240000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-20 23:33:51</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2072,98 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:40:06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:40:06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>240000</v>
+      </c>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,38 +522,42 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G2" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 16:49:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -567,12 +571,8 @@
       <c r="D3" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="n">
         <v>240</v>
       </c>
@@ -586,18 +586,18 @@
         <v>240000</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,14 +634,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -678,14 +678,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,14 +722,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -744,10 +744,10 @@
         <v>240000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>240</v>
@@ -766,14 +766,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -782,42 +782,42 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -854,14 +854,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -898,14 +898,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -941,6 +941,50 @@
         <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -957,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2208,102 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-21 16:49:07</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-21 16:49:07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -546,11 +546,11 @@
         <v>230000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:49:07</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2304,6 +2304,102 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-21 20:04:26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-21 20:04:26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,42 +522,42 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 16:48:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,38 +566,42 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G3" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -611,12 +615,8 @@
       <c r="D4" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="n">
         <v>240</v>
       </c>
@@ -630,18 +630,18 @@
         <v>240000</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -678,14 +678,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,14 +722,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -766,14 +766,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -788,10 +788,10 @@
         <v>240000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>240</v>
@@ -810,14 +810,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -826,42 +826,42 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -898,14 +898,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -942,14 +942,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -985,6 +985,50 @@
         <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1001,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2400,6 +2444,102 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:48:19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:48:19</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -546,11 +546,11 @@
         <v>225000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:48:19</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2540,6 +2540,102 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-22 20:06:02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-22 20:06:02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -527,12 +527,8 @@
       <c r="D2" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="n">
         <v>225</v>
       </c>
@@ -546,18 +542,18 @@
         <v>225000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 16:39:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,42 +562,42 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -610,38 +606,42 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G4" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,12 +655,8 @@
       <c r="D5" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="n">
         <v>240</v>
       </c>
@@ -674,18 +670,18 @@
         <v>240000</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,14 +718,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -766,14 +762,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -810,14 +806,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -832,10 +828,10 @@
         <v>240000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>240</v>
@@ -854,14 +850,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -870,42 +866,42 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -942,14 +938,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -986,14 +982,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1029,6 +1025,50 @@
         <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1045,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2636,6 +2676,98 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-23 16:39:12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-23 16:39:12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -542,11 +542,11 @@
         <v>225000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:39:12</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2768,6 +2768,98 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-23 19:50:04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-23 19:50:04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,38 +522,42 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G2" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 15:56:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -567,12 +571,8 @@
       <c r="D3" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="n">
         <v>225</v>
       </c>
@@ -590,14 +590,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,42 +606,42 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -650,38 +650,42 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G5" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -695,12 +699,8 @@
       <c r="D6" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="2" t="n">
         <v>240</v>
       </c>
@@ -714,18 +714,18 @@
         <v>240000</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -762,14 +762,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -806,14 +806,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -872,10 +872,10 @@
         <v>240000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>240</v>
@@ -894,14 +894,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -910,42 +910,42 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -982,14 +982,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1026,14 +1026,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1069,6 +1069,50 @@
         <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1085,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2860,6 +2904,102 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-24 15:56:21</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-24 15:56:21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -546,11 +546,11 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:56:21</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3000,6 +3000,102 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-24 18:56:58</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-24 18:56:58</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -527,12 +527,8 @@
       <c r="D2" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="n">
         <v>220</v>
       </c>
@@ -546,18 +542,18 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 16:23:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,38 +562,42 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G3" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -611,12 +611,8 @@
       <c r="D4" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="n">
         <v>225</v>
       </c>
@@ -634,14 +630,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -650,42 +646,42 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -694,38 +690,42 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G6" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -739,12 +739,8 @@
       <c r="D7" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="2" t="n">
         <v>240</v>
       </c>
@@ -758,18 +754,18 @@
         <v>240000</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -806,14 +802,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -850,14 +846,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -894,14 +890,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -916,10 +912,10 @@
         <v>240000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>240</v>
@@ -938,14 +934,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -954,42 +950,42 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1026,14 +1022,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1070,14 +1066,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1113,6 +1109,50 @@
         <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1129,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3096,6 +3136,98 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-25 16:23:10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-25 16:23:10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -542,11 +542,11 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-25 16:23:10</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3228,6 +3228,98 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-25 19:18:46</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-25 19:18:46</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,18 +542,18 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-25 19:18:46</t>
+          <t>2026-10-26 17:54:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -567,12 +567,8 @@
       <c r="D3" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="n">
         <v>220</v>
       </c>
@@ -590,14 +586,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,38 +602,42 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G4" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -651,12 +651,8 @@
       <c r="D5" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="n">
         <v>225</v>
       </c>
@@ -674,14 +670,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -690,42 +686,42 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,38 +730,42 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G7" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -779,12 +779,8 @@
       <c r="D8" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="n">
         <v>240</v>
       </c>
@@ -798,18 +794,18 @@
         <v>240000</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -846,14 +842,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -890,14 +886,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -934,14 +930,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -956,10 +952,10 @@
         <v>240000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>240</v>
@@ -978,14 +974,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -994,42 +990,42 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1066,14 +1062,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,14 +1106,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1153,6 +1149,50 @@
         <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1169,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3320,6 +3360,98 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-26 17:54:19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-26 17:54:19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -542,11 +542,11 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-26 17:54:19</t>
+          <t>2026-10-26 21:44:41</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3452,6 +3452,98 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:44:41</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:44:41</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,18 +542,18 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-26 21:44:41</t>
+          <t>2026-10-27 17:13:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -586,14 +586,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-25 19:18:46</t>
+          <t>2026-10-26 21:44:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -607,12 +607,8 @@
       <c r="D4" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="n">
         <v>220</v>
       </c>
@@ -630,14 +626,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,38 +642,42 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G5" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -691,12 +691,8 @@
       <c r="D6" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="2" t="n">
         <v>225</v>
       </c>
@@ -714,14 +710,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -730,42 +726,42 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,38 +770,42 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G8" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -819,12 +819,8 @@
       <c r="D9" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="n">
         <v>240</v>
       </c>
@@ -838,18 +834,18 @@
         <v>240000</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -886,14 +882,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -930,14 +926,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -974,14 +970,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -996,10 +992,10 @@
         <v>240000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>240</v>
@@ -1018,14 +1014,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1034,42 +1030,42 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,14 +1102,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1150,14 +1146,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1193,6 +1189,50 @@
         <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1209,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3544,6 +3584,98 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:13:22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:13:22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -542,11 +542,11 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:13:22</t>
+          <t>2026-10-27 20:58:49</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3676,6 +3676,98 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-27 20:58:49</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-27 20:58:49</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,18 +542,18 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-27 20:58:49</t>
+          <t>2026-10-28 17:46:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -586,14 +586,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-26 21:44:41</t>
+          <t>2026-10-27 20:58:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,14 +626,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-25 19:18:46</t>
+          <t>2026-10-26 21:44:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -647,12 +647,8 @@
       <c r="D5" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="n">
         <v>220</v>
       </c>
@@ -670,14 +666,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -686,38 +682,42 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G6" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -731,12 +731,8 @@
       <c r="D7" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="2" t="n">
         <v>225</v>
       </c>
@@ -754,14 +750,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,42 +766,42 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -814,38 +810,42 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G9" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -859,12 +859,8 @@
       <c r="D10" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="n">
         <v>240</v>
       </c>
@@ -878,18 +874,18 @@
         <v>240000</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -926,14 +922,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -970,14 +966,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,14 +1010,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1036,10 +1032,10 @@
         <v>240000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>240</v>
@@ -1058,14 +1054,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1074,42 +1070,42 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1146,14 +1142,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1190,14 +1186,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1233,6 +1229,50 @@
         <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1249,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3768,6 +3808,98 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:46:54</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:46:54</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -542,11 +542,11 @@
         <v>220000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:46:54</t>
+          <t>2026-10-28 21:41:44</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3900,6 +3900,98 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:41:44</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:41:44</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>220000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,38 +522,42 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>220000</v>
-      </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+        <v>215000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G2" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>220000</v>
+        <v>215000</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>220000</v>
+        <v>215000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-28 21:41:44</t>
+          <t>2026-10-29 17:56:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -586,14 +590,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-27 20:58:49</t>
+          <t>2026-10-28 21:41:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,14 +630,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-26 21:44:41</t>
+          <t>2026-10-27 20:58:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -666,14 +670,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-25 19:18:46</t>
+          <t>2026-10-26 21:44:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,12 +691,8 @@
       <c r="D6" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="2" t="n">
         <v>220</v>
       </c>
@@ -710,14 +710,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -726,38 +726,42 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G7" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -771,12 +775,8 @@
       <c r="D8" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="n">
         <v>225</v>
       </c>
@@ -794,14 +794,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,42 +810,42 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -854,38 +854,42 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G10" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -899,12 +903,8 @@
       <c r="D11" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
       <c r="G11" s="2" t="n">
         <v>240</v>
       </c>
@@ -918,18 +918,18 @@
         <v>240000</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -966,14 +966,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1054,14 +1054,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1076,10 +1076,10 @@
         <v>240000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>240</v>
@@ -1098,14 +1098,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1114,42 +1114,42 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1230,14 +1230,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1273,6 +1273,50 @@
         <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1289,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3992,6 +4036,102 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:56:13</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:56:13</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>215000</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -546,11 +546,11 @@
         <v>215000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:56:13</t>
+          <t>2026-10-29 21:48:24</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4132,6 +4132,102 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-29 21:48:24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-29 21:48:24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>215000</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>-5</v>
@@ -534,30 +534,30 @@
         <v>-5000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-29 21:48:24</t>
+          <t>2026-10-30 17:47:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,38 +566,42 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>220000</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+        <v>215000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G3" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>220000</v>
+        <v>215000</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>220000</v>
+        <v>215000</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-28 21:41:44</t>
+          <t>2026-10-29 21:48:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,14 +634,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-27 20:58:49</t>
+          <t>2026-10-28 21:41:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -670,14 +674,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-26 21:44:41</t>
+          <t>2026-10-27 20:58:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,14 +714,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-25 19:18:46</t>
+          <t>2026-10-26 21:44:41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -731,12 +735,8 @@
       <c r="D7" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="2" t="n">
         <v>220</v>
       </c>
@@ -754,14 +754,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,38 +770,42 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G8" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -815,12 +819,8 @@
       <c r="D9" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="2" t="n">
         <v>225</v>
       </c>
@@ -838,14 +838,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -854,42 +854,42 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -898,38 +898,42 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G11" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -943,12 +947,8 @@
       <c r="D12" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
       <c r="G12" s="2" t="n">
         <v>240</v>
       </c>
@@ -962,18 +962,18 @@
         <v>240000</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1054,14 +1054,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1098,14 +1098,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1120,10 +1120,10 @@
         <v>240000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>240</v>
@@ -1142,14 +1142,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1158,42 +1158,42 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1230,14 +1230,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1274,14 +1274,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1317,6 +1317,50 @@
         <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1333,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4228,6 +4272,102 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:47:39</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:47:39</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>210000</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -546,11 +546,11 @@
         <v>210000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:47:39</t>
+          <t>2026-10-30 21:37:22</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4368,6 +4368,102 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:37:22</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:37:22</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>210000</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,42 +522,42 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>210000</v>
+        <v>200000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-5000</v>
+        <v>-10000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>210000</v>
+        <v>200000</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>210000</v>
+        <v>200000</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-30 21:37:22</t>
+          <t>2026-10-31 17:19:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>-5</v>
@@ -578,30 +578,30 @@
         <v>-5000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-29 21:48:24</t>
+          <t>2026-10-30 21:37:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -610,38 +610,42 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>220000</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+        <v>215000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G4" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>220000</v>
+        <v>215000</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>220000</v>
+        <v>215000</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-28 21:41:44</t>
+          <t>2026-10-29 21:48:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -674,14 +678,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-27 20:58:49</t>
+          <t>2026-10-28 21:41:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -714,14 +718,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-26 21:44:41</t>
+          <t>2026-10-27 20:58:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -754,14 +758,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-25 19:18:46</t>
+          <t>2026-10-26 21:44:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -775,12 +779,8 @@
       <c r="D8" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="n">
         <v>220</v>
       </c>
@@ -798,14 +798,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-24 18:56:58</t>
+          <t>2026-10-25 19:18:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -814,38 +814,42 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+        <v>220000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-5000</v>
+      </c>
       <c r="G9" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-23 19:50:04</t>
+          <t>2026-10-24 18:56:58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -859,12 +863,8 @@
       <c r="D10" s="2" t="n">
         <v>225000</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-5000</v>
-      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
       <c r="G10" s="2" t="n">
         <v>225</v>
       </c>
@@ -882,14 +882,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-22 20:06:02</t>
+          <t>2026-10-23 19:50:04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -898,42 +898,42 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-10000</v>
+        <v>-5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-21 20:04:26</t>
+          <t>2026-10-22 20:06:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -942,38 +942,42 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+        <v>230000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-10000</v>
+      </c>
       <c r="G12" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>240000</v>
+        <v>230000</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-20 23:40:06</t>
+          <t>2026-10-21 20:04:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -987,12 +991,8 @@
       <c r="D13" s="2" t="n">
         <v>240000</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
       <c r="G13" s="2" t="n">
         <v>240</v>
       </c>
@@ -1006,18 +1006,18 @@
         <v>240000</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:00</t>
+          <t>2026-10-20 23:40:06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1054,14 +1054,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:00</t>
+          <t>2026-10-19 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1098,14 +1098,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-17 00:00:00</t>
+          <t>2026-10-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:00:00</t>
+          <t>2026-10-17 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1164,10 +1164,10 @@
         <v>240000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>240</v>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-15 00:00:00</t>
+          <t>2026-10-16 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1202,42 +1202,42 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>245000</v>
+        <v>240000</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:00:00</t>
+          <t>2026-10-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1274,14 +1274,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-14 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1318,14 +1318,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1361,6 +1361,50 @@
         <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:00</t>
         </is>
@@ -1377,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4464,6 +4508,102 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-10-31 17:19:11</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-31 17:19:11</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/silver_rates.xlsx
+++ b/silver_rates.xlsx
@@ -546,11 +546,11 @@
         <v>200000</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-31 17:19:11</t>
+          <t>2026-10-31 20:57:16</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4604,6 +4604,102 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-10-31 20:57:16</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-10-31 20:57:16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.goodreturns.in/silver-rates/chennai.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
